--- a/templates/FAAS_Template.xlsx
+++ b/templates/FAAS_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Videos\FAAS SYSTEM\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\FAAS-System\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA68FB2D-AB67-4EF2-BB0D-20DCFC3D6C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1CF909-09B4-4776-B3D9-2249D515F9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{244C88A5-F8E5-419E-8631-7D0D3F5AAB12}"/>
   </bookViews>
@@ -171,9 +171,6 @@
     <t>Municipal Assessor</t>
   </si>
   <si>
-    <t>RICARDO J. NIEVA</t>
-  </si>
-  <si>
     <t>Appraised/Assessed by:</t>
   </si>
   <si>
@@ -223,6 +220,9 @@
   </si>
   <si>
     <t>ROSALE S. MALALAD</t>
+  </si>
+  <si>
+    <t>RICARDO J. NIEVA REA-0000483</t>
   </si>
 </sst>
 </file>
@@ -655,13 +655,148 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -673,9 +808,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -744,138 +876,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1322,28 +1322,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="62"/>
-      <c r="G1" s="62"/>
-      <c r="H1" s="62"/>
+      <c r="B1" s="76"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A2" s="62" t="s">
+      <c r="A2" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
-      <c r="G2" s="62"/>
-      <c r="H2" s="62"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
     </row>
     <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
@@ -1366,380 +1366,380 @@
       <c r="H4" s="1"/>
     </row>
     <row r="5" spans="1:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="65"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="79"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="66"/>
+      <c r="D6" s="53"/>
       <c r="E6" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="35"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="37"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="82"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="53"/>
       <c r="E7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="35"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="37"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="82"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="46"/>
-      <c r="E8" s="42" t="s">
+      <c r="B8" s="88"/>
+      <c r="C8" s="89"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="51"/>
-      <c r="H8" s="52"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="95"/>
+      <c r="H8" s="96"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="43"/>
-      <c r="B9" s="47"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
+      <c r="A9" s="87"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="92"/>
+      <c r="D9" s="93"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="97"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="99"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="42" t="s">
+      <c r="A10" s="86" t="s">
+        <v>60</v>
+      </c>
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="83"/>
+      <c r="E10" s="86" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="56"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="58"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="102"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="43"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="61"/>
+      <c r="A11" s="87"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="103"/>
+      <c r="G11" s="104"/>
+      <c r="H11" s="105"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="68"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="57"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="34"/>
+      <c r="B13" s="52"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="53"/>
       <c r="E13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="69"/>
-      <c r="G13" s="70"/>
-      <c r="H13" s="71"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="69"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="67"/>
-      <c r="D14" s="68"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="57"/>
       <c r="E14" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="69"/>
-      <c r="G14" s="70"/>
-      <c r="H14" s="71"/>
+        <v>46</v>
+      </c>
+      <c r="F14" s="67"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="69"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="67"/>
-      <c r="D15" s="67"/>
-      <c r="E15" s="67"/>
-      <c r="F15" s="67"/>
-      <c r="G15" s="67"/>
-      <c r="H15" s="68"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="57"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="73"/>
-      <c r="D16" s="73"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="74"/>
+      <c r="B16" s="70"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="72"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="75"/>
-      <c r="C17" s="76"/>
-      <c r="D17" s="76"/>
-      <c r="E17" s="76"/>
-      <c r="F17" s="76"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="77"/>
+      <c r="B17" s="73"/>
+      <c r="C17" s="74"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="75"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="72"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="74"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
+      <c r="G18" s="71"/>
+      <c r="H18" s="72"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="73"/>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="74"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="72"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="66" t="s">
+      <c r="A20" s="56" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="67"/>
-      <c r="C20" s="67"/>
-      <c r="D20" s="67"/>
-      <c r="E20" s="67"/>
-      <c r="F20" s="67"/>
-      <c r="G20" s="67"/>
-      <c r="H20" s="68"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="57"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="32" t="s">
+      <c r="A21" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="B21" s="34"/>
+      <c r="B21" s="53"/>
       <c r="C21" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F21" s="34"/>
-      <c r="G21" s="32" t="s">
+      <c r="F21" s="53"/>
+      <c r="G21" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="H21" s="34"/>
+      <c r="H21" s="53"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="66"/>
-      <c r="B22" s="68"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="57"/>
       <c r="C22" s="14"/>
       <c r="D22" s="15"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="81"/>
+      <c r="E22" s="64"/>
+      <c r="F22" s="65"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="63"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="32"/>
-      <c r="B23" s="34"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="5"/>
       <c r="D23" s="3"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="34"/>
+      <c r="E23" s="52"/>
+      <c r="F23" s="53"/>
+      <c r="G23" s="52"/>
+      <c r="H23" s="53"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="32"/>
-      <c r="B24" s="34"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="53"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="34"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="34"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="53"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="53"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25" s="66" t="s">
+      <c r="A25" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B25" s="68"/>
+      <c r="B25" s="57"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="34"/>
-      <c r="G25" s="82"/>
-      <c r="H25" s="83"/>
+      <c r="E25" s="52"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="61"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" s="66" t="s">
+      <c r="A26" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="67"/>
-      <c r="G26" s="67"/>
-      <c r="H26" s="68"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="57"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B27" s="34"/>
-      <c r="C27" s="32" t="s">
+      <c r="B27" s="53"/>
+      <c r="C27" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="32" t="s">
+      <c r="D27" s="53"/>
+      <c r="E27" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="34"/>
-      <c r="G27" s="32" t="s">
+      <c r="F27" s="53"/>
+      <c r="G27" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="H27" s="34"/>
+      <c r="H27" s="53"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="66"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="66"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="80"/>
-      <c r="H28" s="81"/>
+      <c r="A28" s="56"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="56"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="63"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="32"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="34"/>
+      <c r="A29" s="52"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="52"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="52"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="52"/>
+      <c r="H29" s="53"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="32"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="32"/>
-      <c r="H30" s="34"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="53"/>
+      <c r="C30" s="52"/>
+      <c r="D30" s="53"/>
+      <c r="E30" s="52"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="52"/>
+      <c r="H30" s="53"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="32"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="32"/>
-      <c r="H31" s="34"/>
+      <c r="A31" s="52"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="53"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="53"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="66" t="s">
+      <c r="A32" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B32" s="68"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="84"/>
-      <c r="H32" s="68"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="57"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="86" t="s">
+      <c r="A33" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="86"/>
-      <c r="C33" s="86"/>
-      <c r="D33" s="86"/>
-      <c r="E33" s="86"/>
-      <c r="F33" s="86"/>
-      <c r="G33" s="86"/>
-      <c r="H33" s="86"/>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="53"/>
       <c r="C34" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="32" t="s">
+      <c r="E34" s="52" t="s">
         <v>28</v>
       </c>
-      <c r="F34" s="34"/>
-      <c r="G34" s="32" t="s">
+      <c r="F34" s="53"/>
+      <c r="G34" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="34"/>
+      <c r="H34" s="53"/>
     </row>
     <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="18"/>
@@ -1772,10 +1772,10 @@
       <c r="H37" s="17"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B38" s="68"/>
+      <c r="B38" s="57"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
       <c r="E38" s="6"/>
@@ -1784,16 +1784,16 @@
       <c r="H38" s="17"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A39" s="66" t="s">
+      <c r="A39" s="56" t="s">
         <v>31</v>
       </c>
-      <c r="B39" s="67"/>
-      <c r="C39" s="67"/>
-      <c r="D39" s="67"/>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="68"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="57"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
@@ -1802,26 +1802,26 @@
       <c r="B40" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="34"/>
-      <c r="E40" s="32" t="s">
+      <c r="D40" s="53"/>
+      <c r="E40" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="F40" s="34"/>
-      <c r="G40" s="32" t="s">
+      <c r="F40" s="53"/>
+      <c r="G40" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="H40" s="34"/>
+      <c r="H40" s="53"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="30"/>
       <c r="B41" s="31"/>
       <c r="C41" s="13"/>
       <c r="D41" s="17"/>
-      <c r="E41" s="87"/>
-      <c r="F41" s="88"/>
+      <c r="E41" s="54"/>
+      <c r="F41" s="55"/>
       <c r="G41" s="13"/>
       <c r="H41" s="29"/>
     </row>
@@ -1830,8 +1830,8 @@
       <c r="B42" s="31"/>
       <c r="C42" s="13"/>
       <c r="D42" s="17"/>
-      <c r="E42" s="87"/>
-      <c r="F42" s="88"/>
+      <c r="E42" s="54"/>
+      <c r="F42" s="55"/>
       <c r="G42" s="13"/>
       <c r="H42" s="29"/>
     </row>
@@ -1848,10 +1848,10 @@
       <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A44" s="66" t="s">
+      <c r="A44" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="68"/>
+      <c r="B44" s="57"/>
       <c r="C44" s="6"/>
       <c r="D44" s="17"/>
       <c r="E44" s="6"/>
@@ -1871,40 +1871,40 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="D46" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="9"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="85" t="s">
-        <v>62</v>
-      </c>
-      <c r="B48" s="85"/>
-      <c r="D48" s="86" t="s">
+      <c r="A48" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="51"/>
+      <c r="D48" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="E48" s="86"/>
+      <c r="E48" s="50"/>
       <c r="F48" s="9"/>
-      <c r="G48" s="86" t="s">
+      <c r="G48" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="H48" s="86"/>
+      <c r="H48" s="50"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A49" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="B49" s="38"/>
-      <c r="D49" s="89" t="s">
+      <c r="A49" s="48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B49" s="48"/>
+      <c r="D49" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="E49" s="89"/>
-      <c r="G49" s="89" t="s">
-        <v>53</v>
-      </c>
-      <c r="H49" s="89"/>
+      <c r="E49" s="36"/>
+      <c r="G49" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="H49" s="36"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="21"/>
@@ -1913,15 +1913,15 @@
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B51" s="9"/>
       <c r="C51" s="9"/>
-      <c r="D51" s="90" t="s">
-        <v>50</v>
-      </c>
-      <c r="E51" s="90"/>
+      <c r="D51" s="49" t="s">
+        <v>49</v>
+      </c>
+      <c r="E51" s="49"/>
       <c r="F51" s="9"/>
-      <c r="G51" s="90" t="s">
-        <v>49</v>
-      </c>
-      <c r="H51" s="90"/>
+      <c r="G51" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="H51" s="49"/>
     </row>
     <row r="52" spans="1:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B52" s="9"/>
@@ -1935,75 +1935,75 @@
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B53" s="9"/>
       <c r="C53" s="9"/>
-      <c r="D53" s="86" t="s">
-        <v>45</v>
-      </c>
-      <c r="E53" s="86"/>
+      <c r="D53" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53" s="50"/>
       <c r="F53" s="9"/>
-      <c r="G53" s="85" t="s">
+      <c r="G53" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="H53" s="51"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="D54" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" s="36"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="H53" s="85"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="D54" s="89" t="s">
-        <v>44</v>
-      </c>
-      <c r="E54" s="89"/>
-      <c r="F54" s="11"/>
-      <c r="G54" s="91" t="s">
-        <v>52</v>
-      </c>
-      <c r="H54" s="91"/>
+      <c r="H54" s="37"/>
     </row>
     <row r="55" spans="1:8" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="92"/>
-      <c r="C56" s="92"/>
-      <c r="D56" s="92"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
     </row>
     <row r="57" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="93"/>
-      <c r="B57" s="94"/>
-      <c r="C57" s="94"/>
-      <c r="D57" s="94"/>
-      <c r="E57" s="94"/>
-      <c r="F57" s="94"/>
-      <c r="G57" s="94"/>
-      <c r="H57" s="95"/>
+      <c r="A57" s="39"/>
+      <c r="B57" s="40"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="40"/>
+      <c r="E57" s="40"/>
+      <c r="F57" s="40"/>
+      <c r="G57" s="40"/>
+      <c r="H57" s="41"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A58" s="96"/>
-      <c r="B58" s="97"/>
-      <c r="C58" s="97"/>
-      <c r="D58" s="97"/>
-      <c r="E58" s="97"/>
-      <c r="F58" s="97"/>
-      <c r="G58" s="97"/>
-      <c r="H58" s="98"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="43"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="43"/>
+      <c r="H58" s="44"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A59" s="96"/>
-      <c r="B59" s="97"/>
-      <c r="C59" s="97"/>
-      <c r="D59" s="97"/>
-      <c r="E59" s="97"/>
-      <c r="F59" s="97"/>
-      <c r="G59" s="97"/>
-      <c r="H59" s="98"/>
+      <c r="A59" s="42"/>
+      <c r="B59" s="43"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="43"/>
+      <c r="H59" s="44"/>
     </row>
     <row r="60" spans="1:8" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="99"/>
-      <c r="B60" s="100"/>
-      <c r="C60" s="100"/>
-      <c r="D60" s="100"/>
-      <c r="E60" s="100"/>
-      <c r="F60" s="100"/>
-      <c r="G60" s="100"/>
-      <c r="H60" s="101"/>
+      <c r="A60" s="45"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="47"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
@@ -2018,100 +2018,85 @@
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="E62" s="31"/>
+      <c r="F62" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="G62" s="35"/>
+      <c r="H62" s="26"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A63" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="B62" s="102"/>
-      <c r="C62" s="102"/>
-      <c r="D62" s="23" t="s">
+      <c r="B63" s="33"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="E62" s="31"/>
-      <c r="F62" s="103" t="s">
+      <c r="E63" s="34"/>
+      <c r="F63" s="35" t="s">
         <v>58</v>
       </c>
-      <c r="G62" s="103"/>
-      <c r="H62" s="26"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="104" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="105"/>
-      <c r="C63" s="105"/>
-      <c r="D63" s="104" t="s">
-        <v>55</v>
-      </c>
-      <c r="E63" s="102"/>
-      <c r="F63" s="103" t="s">
+      <c r="G63" s="35"/>
+      <c r="H63" s="26"/>
+    </row>
+    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="32"/>
+      <c r="B64" s="33"/>
+      <c r="C64" s="33"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="34"/>
+      <c r="F64" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="G63" s="103"/>
-      <c r="H63" s="26"/>
-    </row>
-    <row r="64" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="104"/>
-      <c r="B64" s="105"/>
-      <c r="C64" s="105"/>
-      <c r="D64" s="104"/>
-      <c r="E64" s="102"/>
-      <c r="F64" s="103" t="s">
-        <v>60</v>
-      </c>
-      <c r="G64" s="103"/>
+      <c r="G64" s="35"/>
       <c r="H64" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="100">
-    <mergeCell ref="A63:A64"/>
-    <mergeCell ref="B63:C64"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="E63:E64"/>
-    <mergeCell ref="F63:G63"/>
-    <mergeCell ref="F64:G64"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="G54:H54"/>
-    <mergeCell ref="B56:D56"/>
-    <mergeCell ref="A57:H60"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="F62:G62"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="D51:E51"/>
-    <mergeCell ref="G51:H51"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="G53:H53"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="E40:F40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="D48:E48"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:H39"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="G29:H29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="F7:H7"/>
+    <mergeCell ref="B10:D11"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:D9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="F8:H9"/>
+    <mergeCell ref="F10:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="F13:H13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="G23:H23"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
@@ -2127,46 +2112,61 @@
     <mergeCell ref="C27:D27"/>
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="G27:H27"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="F13:H13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="B10:D11"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:D9"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="F8:H9"/>
-    <mergeCell ref="F10:H11"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="E34:F34"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="G53:H53"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="E40:F40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="D51:E51"/>
+    <mergeCell ref="G51:H51"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="G54:H54"/>
+    <mergeCell ref="B56:D56"/>
+    <mergeCell ref="A57:H60"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="F62:G62"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="B63:C64"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="E63:E64"/>
+    <mergeCell ref="F63:G63"/>
+    <mergeCell ref="F64:G64"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="14" scale="95" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="14" scale="95" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>